--- a/SEM 7/Progress.xlsx
+++ b/SEM 7/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C768529B-BD13-445C-AA54-62A0835B5132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0525B279-142F-482E-B5E0-36772ADA0D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="24">
   <si>
     <t>EXP1</t>
   </si>
@@ -78,40 +78,10 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>ASS3</t>
-  </si>
-  <si>
-    <t>ASS4</t>
-  </si>
-  <si>
-    <t>ASS5</t>
-  </si>
-  <si>
-    <t>TUT1</t>
-  </si>
-  <si>
-    <t>TUT2</t>
-  </si>
-  <si>
-    <t>TUT3</t>
-  </si>
-  <si>
-    <t>TUT4</t>
-  </si>
-  <si>
-    <t>TUT5</t>
-  </si>
-  <si>
-    <t>TUT6</t>
-  </si>
-  <si>
     <t>EXP14</t>
   </si>
   <si>
     <t>EXP15</t>
-  </si>
-  <si>
-    <t>ASS6</t>
   </si>
   <si>
     <t>DS</t>
@@ -539,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F32"/>
+  <dimension ref="B2:F22"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1"/>
@@ -549,16 +519,16 @@
   <sheetData>
     <row r="2" spans="2:6" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -566,13 +536,13 @@
         <v>0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>15</v>
@@ -583,13 +553,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>15</v>
@@ -600,13 +570,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>15</v>
@@ -617,13 +587,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>15</v>
@@ -634,13 +604,13 @@
         <v>4</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>15</v>
@@ -651,13 +621,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>15</v>
@@ -668,13 +638,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>15</v>
@@ -685,13 +655,13 @@
         <v>7</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>15</v>
@@ -702,13 +672,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>15</v>
@@ -719,7 +689,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>15</v>
@@ -736,7 +706,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>15</v>
@@ -752,8 +722,8 @@
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>33</v>
+      <c r="C15" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>15</v>
@@ -770,7 +740,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>15</v>
@@ -784,10 +754,10 @@
     </row>
     <row r="17" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>15</v>
@@ -801,10 +771,10 @@
     </row>
     <row r="18" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>15</v>
@@ -827,14 +797,14 @@
       <c r="B20" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>15</v>
+      <c r="C20" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>15</v>
+      <c r="E20" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>15</v>
@@ -850,185 +820,15 @@
       <c r="D21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>15</v>
+      <c r="E21" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="3"/>
-    </row>
-    <row r="27" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="B22" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/SEM 7/Progress.xlsx
+++ b/SEM 7/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0525B279-142F-482E-B5E0-36772ADA0D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9994AD-C75B-4010-B393-3EC84803D28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="25">
   <si>
     <t>EXP1</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>Incomplete</t>
+  </si>
+  <si>
+    <t>Mini Project</t>
   </si>
 </sst>
 </file>
@@ -509,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F22"/>
+  <dimension ref="B2:F23"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1"/>
@@ -643,8 +646,8 @@
       <c r="D10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>23</v>
+      <c r="E10" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>15</v>
@@ -660,8 +663,8 @@
       <c r="D11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>23</v>
+      <c r="E11" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>15</v>
@@ -694,8 +697,8 @@
       <c r="D13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>15</v>
+      <c r="E13" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>15</v>
@@ -830,6 +833,23 @@
     <row r="22" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B22" s="3"/>
     </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SEM 7/Progress.xlsx
+++ b/SEM 7/Progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9994AD-C75B-4010-B393-3EC84803D28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700079B2-F6F5-4A11-8B48-A7116F546E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="24">
   <si>
     <t>EXP1</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>Completed</t>
-  </si>
-  <si>
-    <t>Incomplete</t>
   </si>
   <si>
     <t>Mini Project</t>
@@ -109,7 +106,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,21 +158,8 @@
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Microsoft JhengHei UI"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -192,11 +176,6 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -207,13 +186,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -226,13 +204,9 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="3">
     <cellStyle name="Accent3" xfId="1" builtinId="37"/>
-    <cellStyle name="Bad" xfId="3" builtinId="27"/>
     <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -680,8 +654,8 @@
       <c r="D12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>23</v>
+      <c r="E12" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>15</v>
@@ -697,8 +671,8 @@
       <c r="D13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>23</v>
+      <c r="E13" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>15</v>
@@ -776,8 +750,8 @@
       <c r="B18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>23</v>
+      <c r="C18" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>15</v>
@@ -835,13 +809,13 @@
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>15</v>
+      <c r="C23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>15</v>

--- a/SEM 7/Progress.xlsx
+++ b/SEM 7/Progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700079B2-F6F5-4A11-8B48-A7116F546E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0905CD51-CE83-4C16-BBE1-6C66C5142547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="25">
   <si>
     <t>EXP1</t>
   </si>
@@ -100,13 +100,16 @@
   </si>
   <si>
     <t>Mini Project</t>
+  </si>
+  <si>
+    <t>Incomplete</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,8 +161,21 @@
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,6 +192,11 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -186,12 +207,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -204,9 +226,13 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Accent3" xfId="1" builtinId="37"/>
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
     <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -777,8 +803,8 @@
       <c r="C20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>15</v>
+      <c r="D20" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>22</v>
@@ -791,11 +817,11 @@
       <c r="B21" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>15</v>
+      <c r="C21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>22</v>
@@ -814,14 +840,14 @@
       <c r="C23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>22</v>
+      <c r="D23" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>15</v>
+      <c r="F23" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/SEM 7/Progress.xlsx
+++ b/SEM 7/Progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0905CD51-CE83-4C16-BBE1-6C66C5142547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F147BA9-272F-41DA-9741-1DC16F7AD35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="24">
   <si>
     <t>EXP1</t>
   </si>
@@ -100,16 +100,13 @@
   </si>
   <si>
     <t>Mini Project</t>
-  </si>
-  <si>
-    <t>Incomplete</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,21 +158,8 @@
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -192,11 +176,6 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -207,13 +186,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -226,13 +204,9 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="3">
     <cellStyle name="Accent3" xfId="1" builtinId="37"/>
-    <cellStyle name="Bad" xfId="3" builtinId="27"/>
     <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -820,8 +794,8 @@
       <c r="C21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>24</v>
+      <c r="D21" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>22</v>
@@ -840,8 +814,8 @@
       <c r="C23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>24</v>
+      <c r="D23" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>15</v>
